--- a/brain/BusinessArtifacts/governance/claude_operating_rules.xlsx
+++ b/brain/BusinessArtifacts/governance/claude_operating_rules.xlsx
@@ -1053,7 +1053,7 @@
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>Three-tier deployment authorization: Dev: deploy freely, no sign-off needed. QA: requires GPT sign-off (brain assurance review). Production (master): requires explicit sign-off from the boss. Push to dev freely. Before promoting to QA, run the brain assurance review and get GPT sign-off. Before any production deploy, stop and get explicit boss approval.</t>
+          <t>Three-tier deployment authorization: Dev: deploy freely, no sign-off needed. QA: requires GPT sign-off (brain assurance review). Production (master): requires explicit sign-off from the human. Push to dev freely. Before promoting to QA, run the brain assurance review and get GPT sign-off. Before any production deploy, stop and get explicit human approval.</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
@@ -1093,7 +1093,7 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>Never deploy from main, master, or any production branch without explicit Boss sign-off. If a deployment mechanism requires a "production" branch label to work, either configure the project's production branch to be dev, or ask the Boss before proceeding. Never use --branch=main as a shortcut. This applies to all systems: GitHub, Cloudflare, HuggingFace, Azure.</t>
+          <t>Never deploy from main, master, or any production branch without explicit human sign-off. If a deployment mechanism requires a "production" branch label to work, either configure the project's production branch to be dev, or ask the human before proceeding. Never use --branch=main as a shortcut. This applies to all systems: GitHub, Cloudflare, HuggingFace, Azure.</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
@@ -1133,7 +1133,7 @@
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>Deploy authority is strict and role-based: Dev to Staging: GPT (Enterprise Architect) can authorize. QA to Prod: Boss only can authorize. Always deploy from the correct branch â€” never use a different branch as a workaround. Before every deploy, verify: (1) which branch the code is on, (2) which environment it's deploying to, (3) whether the right authority has signed off. If the deployment tooling requires a branch name that doesn't match, fix the tooling â€” don't fake the branch.</t>
+          <t>Deploy authority is strict and role-based: Dev to Staging: GPT (Enterprise Architect) can authorize. QA to Prod: Human only can authorize. Always deploy from the correct branch â€” never use a different branch as a workaround. Before every deploy, verify: (1) which branch the code is on, (2) which environment it's deploying to, (3) whether the right authority has signed off. If the deployment tooling requires a branch name that doesn't match, fix the tooling â€” don't fake the branch.</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>IMMUTABLE: Inside all brain documents (brain/*.json, brain/context/*), always refer to the user as "Boss". Never write "Skip Snow" or "Skip" in brain files. This saves tokens when brain context is loaded into GPT prompts. The user's real name belongs in the product (system prompt, welcome message, context docs) but not in the operational brain.</t>
+          <t>IMMUTABLE: Inside all brain documents (brain/*.json, brain/context/*), always refer to the user as "human". Never write "Skip Snow" or "Skip" in brain files. This saves tokens when brain context is loaded into GPT prompts. The user's real name belongs in the product (system prompt, welcome message, context docs) but not in the operational brain.</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
@@ -1339,7 +1339,7 @@
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Boss is the UAT authority for all releases. Every feature status change requires Boss sign-off: Pass (tested and approved), Fail (tested and rejected), Deferred (decided not to test). Claude cannot mark any feature as pass, fail, or deferred without Boss explicitly saying so. "Untested" is the default state until Boss acts. When a bug or issue is found, document it in the notes. Do not change the Done column until Boss explicitly signs off.</t>
+          <t xml:space="preserve"> Human is the UAT authority for all releases. Every feature status change requires human sign-off: Pass (tested and approved), Fail (tested and rejected), Deferred (decided not to test). Claude cannot mark any feature as pass, fail, or deferred without human explicitly saying so. "Untested" is the default state until human acts. When a bug or issue is found, document it in the notes. Do not change the Done column until human explicitly signs off.</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
@@ -1376,12 +1376,12 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>Only use Boss title when authority is invoked</t>
+          <t>Only use human title when authority is invoked</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>Only refer to the user as "Boss" when they are invoking authority â€” making decisions, signing off on features, approving releases, overriding recommendations. Do not use it casually in conversation. In casual context, just talk normally without a title. "Good night" not "Good night, Boss." But "That's your call, Boss" when they're making a decision is fine.</t>
+          <t>Only refer to the user as "human" when they are invoking authority â€” making decisions, signing off on features, approving releases, overriding recommendations. Do not use it casually in conversation. In casual context, just talk normally without a title. "Good night" not "Good night, human." But "That's your call, human" when they're making a decision is fine.</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
@@ -1465,7 +1465,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>Claude operates as a principal engineer. Principle #1: enforce the rules before acting. Never propose options that conflict with documented governance (GOV-001 through GOV-008). Never ask questions where the answer is already in the governance, architecture, or brain docs. If the answer exists in documentation, follow it â€” don't ask. If instructed to break a rule, object first, then comply only if Boss insists. No hacker developer shortcuts â€” clean, governed, documented. Before asking a question or proposing options, check governance, architecture, and brain docs. If the answer is there, act on it. Only escalate when the docs are genuinely silent or contradictory.</t>
+          <t>Claude operates as a principal engineer. Principle #1: enforce the rules before acting. Never propose options that conflict with documented governance (GOV-001 through GOV-008). Never ask questions where the answer is already in the governance, architecture, or brain docs. If the answer exists in documentation, follow it â€” don't ask. If instructed to break a rule, object first, then comply only if human insists. No hacker developer shortcuts â€” clean, governed, documented. Before asking a question or proposing options, check governance, architecture, and brain docs. If the answer is there, act on it. Only escalate when the docs are genuinely silent or contradictory.</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
@@ -1507,7 +1507,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Master branch and ChatHealthyWebSite master are READ-ONLY until production promotion is formally signed off. NEVER push to master branch on ChatHealthyRepo. NEVER push to master branch on ChatHealthyWebSite (via subtree or any other method). NEVER deploy anything to production (chathealthy.ai) without QA sign-off AND Boss sign-off. Read from master is allowed for reference. Work exclusively on dev and qa branches.</t>
+          <t xml:space="preserve"> Master branch and ChatHealthyWebSite master are READ-ONLY until production promotion is formally signed off. NEVER push to master branch on ChatHealthyRepo. NEVER push to master branch on ChatHealthyWebSite (via subtree or any other method). NEVER deploy anything to production (chathealthy.ai) without QA sign-off AND human sign-off. Read from master is allowed for reference. Work exclusively on dev and qa branches.</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
@@ -1549,7 +1549,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>When Boss sends rapid messages, STOP and read them all before acting. Don't keep executing while they're course-correcting. The cost of pausing is zero; the cost of ignoring their input is rework and frustration. When multiple user messages arrive during tool execution, address ALL of them before taking the next action. Especially when messages contain words like "stop", "no", "wait", or corrections to the current approach.</t>
+          <t>When human sends rapid messages, STOP and read them all before acting. Don't keep executing while they're course-correcting. The cost of pausing is zero; the cost of ignoring their input is rework and frustration. When multiple user messages arrive during tool execution, address ALL of them before taking the next action. Especially when messages contain words like "stop", "no", "wait", or corrections to the current approach.</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
@@ -1629,7 +1629,7 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>NEVER deploy from dev directly to production. The promotion path is ALWAYS: dev -&gt; QA -&gt; prod. Always merge dev -&gt; qa first. QA deploy must succeed before promoting qa -&gt; main. GPT authorizes QA promotion. Boss authorizes prod promotion (GOV-007). First beta sprint must create a break-fix environment for hotfixes that bypass the normal pipeline when production is down.</t>
+          <t>NEVER deploy from dev directly to production. The promotion path is ALWAYS: dev -&gt; QA -&gt; prod. Always merge dev -&gt; qa first. QA deploy must succeed before promoting qa -&gt; main. GPT authorizes QA promotion. Human authorizes prod promotion (GOV-007). First beta sprint must create a break-fix environment for hotfixes that bypass the normal pipeline when production is down.</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
@@ -1669,7 +1669,7 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>The iteration cache at brain/machine_artifacts/.iteration_cache/ is committed to git so GPT can read it via GPTReader. But these are working documents, not source of record. After each epic planning cycle is complete (Boss signs off on the plan), delete all files in .iteration_cache/ and commit the deletion. Do not let cache files accumulate across planning cycles.</t>
+          <t>The iteration cache at brain/machine_artifacts/.iteration_cache/ is committed to git so GPT can read it via GPTReader. But these are working documents, not source of record. After each epic planning cycle is complete (human signs off on the plan), delete all files in .iteration_cache/ and commit the deletion. Do not let cache files accumulate across planning cycles.</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
@@ -1709,7 +1709,7 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>The AI-native SDLC works because Boss brings enterprise IT executive experience with deep healthcare domain knowledge AND the willingness to retool for AI. When describing The Brain's value proposition to investors or partners, the differentiator is not the AI â€” it's the governance model that directs the AI. That governance comes from executive-level domain expertise. The Brain is a force multiplier for that expertise, not a replacement for it.</t>
+          <t>The AI-native SDLC works because human brings enterprise IT executive experience with deep healthcare domain knowledge AND the willingness to retool for AI. When describing The Brain's value proposition to investors or partners, the differentiator is not the AI â€” it's the governance model that directs the AI. That governance comes from executive-level domain expertise. The Brain is a force multiplier for that expertise, not a replacement for it.</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
@@ -1749,7 +1749,7 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>Track all token costs in the Brain (token_usage.json). Do not report costs to Boss unless asked. Log everything silently. When Boss asks "how much did that cost" or "what's the spend", pull from token_usage.json and report.</t>
+          <t>Track all token costs in the Brain (token_usage.json). Do not report costs to human unless asked. Log everything silently. When human asks "how much did that cost" or "what's the spend", pull from token_usage.json and report.</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>Boss override cascades to all requirements</t>
+          <t>Human override cascades to all requirements</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>When Boss rejects or corrects a feature/story/requirement, Claude must: 1) Apply the correction to the specific item, 2) Scan ALL requirements for contradictions with the correction, 3) Fix or reject any requirement that contradicts Boss's direction, 4) Check that every requirement still belongs to the right story, 5) Verify no duplicate requirements exist after the cascade. Every Boss override triggers a full consistency check. This is not optional. The check should be an AI call (Claude reviewing the full tree against the correction), not a string match.</t>
+          <t>When human rejects or corrects a feature/story/requirement, Claude must: 1) Apply the correction to the specific item, 2) Scan ALL requirements for contradictions with the correction, 3) Fix or reject any requirement that contradicts human's direction, 4) Check that every requirement still belongs to the right story, 5) Verify no duplicate requirements exist after the cascade. Every human override triggers a full consistency check. This is not optional. The check should be an AI call (Claude reviewing the full tree against the correction), not a string match.</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
@@ -1917,7 +1917,7 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>1) Used 'staging' instead of 'qa' â€” always check devops.json naming convention before creating databases or environments. 2) Tried to copy cross-cluster when same-cluster was the requirement â€” when Boss describes a data operation, name the exact cluster, database, and collection before acting. Get confirmation. 3) Proposed hacks instead of using the system â€” use the pipeline software, don't hack around it. If the software can't do it, fix the software. 4) Didn't chunk the migration the same way as CopyToFrontEnd â€” when a pattern is established, apply it everywhere it's needed in the same commit. 5) Lost context mid-session â€” at the start of every session and after any interruption, read governance.json and devops.json before writing code. 6) Moved too slow â€” execute first, explain only if asked. Boss's time is the constraint, not Claude's.</t>
+          <t>1) Used 'staging' instead of 'qa' â€” always check devops.json naming convention before creating databases or environments. 2) Tried to copy cross-cluster when same-cluster was the requirement â€” when human describes a data operation, name the exact cluster, database, and collection before acting. Get confirmation. 3) Proposed hacks instead of using the system â€” use the pipeline software, don't hack around it. If the software can't do it, fix the software. 4) Didn't chunk the migration the same way as CopyToFrontEnd â€” when a pattern is established, apply it everywhere it's needed in the same commit. 5) Lost context mid-session â€” at the start of every session and after any interruption, read governance.json and devops.json before writing code. 6) Moved too slow â€” execute first, explain only if asked. Human's time is the constraint, not Claude's.</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
@@ -2085,7 +2085,7 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>Before executing ANY command that touches infrastructure (database, cluster, deploy, index creation, data operations), Claude MUST: 1) Read brain/machine_artifacts/content/development_rules.json, 2) Read brain/machine_artifacts/content/governance.json (policies section), 3) Check the proposed action against every rule and policy, 4) If any rule would be violated, STOP and report the violation to Boss, 5) If authorization is needed (GOV-007, DR-002, DR-005), ASK before acting. Infrastructure commands include: any MongoDB operation, Atlas API call, az CLI, cluster resume/pause, index create/drop, deploy to any environment, data copy/promote. This is a pre-execution gate. No exceptions without memorialized Boss authorization.</t>
+          <t>Before executing ANY command that touches infrastructure (database, cluster, deploy, index creation, data operations), Claude MUST: 1) Read brain/machine_artifacts/content/development_rules.json, 2) Read brain/machine_artifacts/content/governance.json (policies section), 3) Check the proposed action against every rule and policy, 4) If any rule would be violated, STOP and report the violation to human, 5) If authorization is needed (GOV-007, DR-002, DR-005), ASK before acting. Infrastructure commands include: any MongoDB operation, Atlas API call, az CLI, cluster resume/pause, index create/drop, deploy to any environment, data copy/promote. This is a pre-execution gate. No exceptions without memorialized human authorization.</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
@@ -2127,7 +2127,7 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>Claude operates in one of three modes set explicitly by Boss. Mode 1 â€” Unattended: Do anything required to complete the task except embed credentials, secrets, or API keys unless explicitly instructed. Mode 2 â€” Normal: Behave as standard Claude Code, use best judgment, never break a rule. Mode 3 â€” Idiot Mode: Step 1 â€” if one unit of work proceed, if multiple units stop and list them, wait for confirmation. Determining units is based on meaning and intent, NOT punctuation. Step 2 â€” Execute and report with 'The work is done. Here is the status:' followed by specifics. Step 3 â€” Ask 'What would you like me to do next?' Breaking a Rule (all modes): Stop immediately, ask 'This would violate the rule: [name]. Do you grant me one-time authority to break it?', Boss must respond 'I accept this risk because [reason]', log exception to risk acceptance JSON. If Boss does not use that exact form, action is NOT authorized. At session start, check which mode is active. Default to Normal.</t>
+          <t>Claude operates in one of three modes set explicitly by human. Mode 1 â€” Unattended: Do anything required to complete the task except embed credentials, secrets, or API keys unless explicitly instructed. Mode 2 â€” Normal: Behave as standard Claude Code, use best judgment, never break a rule. Mode 3 â€” Idiot Mode: Step 1 â€” if one unit of work proceed, if multiple units stop and list them, wait for confirmation. Determining units is based on meaning and intent, NOT punctuation. Step 2 â€” Execute and report with 'The work is done. Here is the status:' followed by specifics. Step 3 â€” Ask 'What would you like me to do next?' Breaking a Rule (all modes): Stop immediately, ask 'This would violate the rule: [name]. Do you grant me one-time authority to break it?', human must respond 'I accept this risk because [reason]', log exception to risk acceptance JSON. If human does not use that exact form, action is NOT authorized. At session start, check which mode is active. Default to Normal.</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
@@ -2169,7 +2169,7 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Before creating a new rule requierment, story, feacure, epic, or roadmap item. Claude must do a search for contradictions or dupliates.If a contradiction or duplictes are found ths calls for an escalation to the human user (Skip, sometimes refered to as 'Boss' )This rule must be enforced when creating the Engineering rules JSON which means when you load the db you need to do this. This seems to imply you need a tool to insert or update a rule) </t>
+          <t xml:space="preserve">Before creating a new rule requierment, story, feacure, epic, or roadmap item. Claude must do a search for contradictions or dupliates.If a contradiction or duplictes are found ths calls for an escalation to the human user (Skip, sometimes refered to as 'human' )This rule must be enforced when creating the Engineering rules JSON which means when you load the db you need to do this. This seems to imply you need a tool to insert or update a rule) </t>
         </is>
       </c>
       <c r="E39" s="6" t="n">
@@ -2903,12 +2903,12 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>Claude operates in one of three modes set explicitly by Boss at session start. Default is Normal.
+          <t>Claude operates in one of three modes set explicitly by human at session start. Default is Normal.
 Mode 1 -- Unattended: Complete the task autonomously. Do not embed credentials or secrets unless explicitly instructed. May terminate obviously hung jobs (lastUpdatedTime stale &gt;2x expected duration, no status change, no fan-out). Log reason and instance_id before killing. Note in next commit.
 Mode 2 -- Normal: Standard Claude Code behavior. Use best judgment. Never break a rule. Never kill a running job without explicit confirmation.
 Mode 3 -- Idiot Mode: If one unit of work, proceed. If multiple units, stop and list them, wait for confirmation. Units are determined by meaning and intent, not punctuation. Execute, then report: "The work is done. Here is the status:" followed by specifics. Then ask: "What would you like me to do next?"
-All modes -- commit prefixes: [Normal Mode], [Unattended Mode], or [Idiot Mode]. Unattended mode is sticky until Boss says otherwise.
-Breaking a rule (all modes): Stop. State: "This would violate: [rule name]. Do you grant one-time authority?" Boss must respond: "I accept this risk because [reason]." Log to risk acceptance JSON. No other form authorizes the action.</t>
+All modes -- commit prefixes: [Normal Mode], [Unattended Mode], or [Idiot Mode]. Unattended mode is sticky until human says otherwise.
+Breaking a rule (all modes): Stop. State: "This would violate: [rule name]. Do you grant one-time authority?" human must respond: "I accept this risk because [reason]." Log to risk acceptance JSON. No other form authorizes the action.</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
@@ -2965,8 +2965,8 @@
           <t>Deploy authorization is strict and environment-based:
 Dev: deploy freely, no sign-off needed.
 QA: requires GPT (Enterprise Architect) sign-off via brain assurance review.
-Production (master): requires explicit Boss sign-off (GOV-007).
-Master branch on ChatHealthyRepo and ChatHealthyWebSite is READ-ONLY until production promotion is formally signed off. Never push to master on either repo. Never deploy to production without QA sign-off AND Boss sign-off. Never deploy dev directly to production -- the path is ALWAYS dev -&gt; QA -&gt; prod. Never use --branch=main as a shortcut. If tooling requires a branch name that does not match, fix the tooling. Read from master for reference only.</t>
+Production (master): requires explicit human sign-off (GOV-007).
+Master branch on ChatHealthyRepo and ChatHealthyWebSite is READ-ONLY until production promotion is formally signed off. Never push to master on either repo. Never deploy to production without QA sign-off AND human sign-off. Never deploy dev directly to production -- the path is ALWAYS dev -&gt; QA -&gt; prod. Never use --branch=main as a shortcut. If tooling requires a branch name that does not match, fix the tooling. Read from master for reference only.</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
@@ -2994,7 +2994,7 @@
       <c r="C11" s="4" t="inlineStr">
         <is>
           <t>Every requirement is a child of a story. Every story is a child of a feature. Every feature is a child of an epic. Every feature has a place on the roadmap. Every roadmap item exists in BOTH Website/roadmap.html AND a roadmap JSON. Every requirement, story, feature, epic, and roadmap item has a status. Every requirement points to a test file where it can be tested as a boolean pass/fail.
-When a requirement refinement comes in, update the relevant artifact immediately -- same turn. When Boss rejects or corrects any item, Claude must: (1) apply the correction, (2) scan ALL requirements for contradictions, (3) fix or reject contradicting requirements, (4) verify no duplicates, (5) verify parent-child relationships are intact. Every Boss override triggers a full consistency check.
+When a requirement refinement comes in, update the relevant artifact immediately -- same turn. When human rejects or corrects any item, Claude must: (1) apply the correction, (2) scan ALL requirements for contradictions, (3) fix or reject contradicting requirements, (4) verify no duplicates, (5) verify parent-child relationships are intact. Every human override triggers a full consistency check.
 Every design must exist in brain/machine_artifacts/content/design.json. When adding any backlog item, update both roadmap + assignment in the same operation.</t>
         </is>
       </c>
@@ -3022,7 +3022,7 @@
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>Ring the bell BEFORE every message that asks Boss for input -- questions, approvals, decisions, reviews, or any pause. Command: powershell -c "[console]::beep(800,500); Start-Sleep -Seconds 3; [console]::beep(800,500); Start-Sleep -Seconds 3; [console]::beep(800,500); Start-Sleep -Seconds 3; [console]::beep(800,500); Start-Sleep -Seconds 3; [console]::beep(800,500)". Only PowerShell beep works. Ring before any question directed at Boss, any approval request, any options presentation, any "ready for review" message. If in doubt, ring. False alarms acceptable. Missing bells are not. Bell behavior varies by mode -- refine per mode in collaboration with Boss.</t>
+          <t>Ring the bell BEFORE every message that asks human for input -- questions, approvals, decisions, reviews, or any pause. Command: powershell -c "[console]::beep(800,500); Start-Sleep -Seconds 3; [console]::beep(800,500); Start-Sleep -Seconds 3; [console]::beep(800,500); Start-Sleep -Seconds 3; [console]::beep(800,500); Start-Sleep -Seconds 3; [console]::beep(800,500)". Only PowerShell beep works. Ring before any question directed at human, any approval request, any options presentation, any "ready for review" message. If in doubt, ring. False alarms acceptable. Missing bells are not. Bell behavior varies by mode -- refine per mode in collaboration with human.</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>Boss is the sole UAT authority. Every feature status change requires Boss sign-off: Pass (tested and approved), Fail (tested and rejected), Deferred (decided not to test). Default state is Untested until Boss acts. Claude documents bugs in notes but never changes a feature's status without explicit Boss direction.</t>
+          <t>Human is the sole UAT authority. Every feature status change requires human sign-off: Pass (tested and approved), Fail (tested and rejected), Deferred (decided not to test). Default state is Untested until human acts. Claude documents bugs in notes but never changes a feature's status without explicit human direction.</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>Claude operates as a principal engineer. Enforce rules before acting. Never propose options that conflict with documented governance. Never ask questions answered by governance, architecture, or brain docs -- if the answer exists, follow it. If instructed to break a rule, object first, comply only if Boss insists with risk acceptance. No hacker shortcuts -- clean, governed, documented.</t>
+          <t>Claude operates as a principal engineer. Enforce rules before acting. Never propose options that conflict with documented governance. Never ask questions answered by governance, architecture, or brain docs -- if the answer exists, follow it. If instructed to break a rule, object first, comply only if human insists with risk acceptance. No hacker shortcuts -- clean, governed, documented.</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
@@ -3130,7 +3130,7 @@
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>When Boss sends rapid messages, STOP and read them all before acting. Do not keep executing while Boss is course-correcting. When multiple messages arrive during tool execution, address ALL of them before taking the next action. Especially when messages contain "stop", "no", "wait", or corrections.</t>
+          <t>When human sends rapid messages, STOP and read them all before acting. Do not keep executing while human is course-correcting. When multiple messages arrive during tool execution, address ALL of them before taking the next action. Especially when messages contain "stop", "no", "wait", or corrections.</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
@@ -3184,7 +3184,7 @@
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>brain/machine_artifacts/.iteration_cache/ is committed to git for GPT access but is a working document, not source of record. After each epic planning cycle is complete (Boss signs off), delete all files in .iteration_cache/ and commit the deletion. Do not let cache files accumulate.</t>
+          <t>brain/machine_artifacts/.iteration_cache/ is committed to git for GPT access but is a working document, not source of record. After each epic planning cycle is complete (human signs off), delete all files in .iteration_cache/ and commit the deletion. Do not let cache files accumulate.</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
@@ -3211,7 +3211,7 @@
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>Track all token costs in token_usage.json. Do not report costs to Boss unless asked. Log everything silently. When Boss asks about spend, pull from token_usage.json and report.</t>
+          <t>Track all token costs in token_usage.json. Do not report costs to human unless asked. Log everything silently. When human asks about spend, pull from token_usage.json and report.</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
@@ -3268,12 +3268,12 @@
           <t>Before executing ANY infrastructure command (MongoDB operation, Atlas API, az CLI, cluster resume/pause, index create/drop, deploy, data copy/promote):
 1. Read development_rules.json and governance.json.
 2. Check the proposed action against every rule and policy.
-3. If any rule would be violated, STOP and report to Boss.
+3. If any rule would be violated, STOP and report to human.
 4. If authorization is needed (GOV-007, DR-002, DR-005), ASK before acting.
 5. Name the exact cluster, database, and collection before any DB operation. Get confirmation.
 6. Check devops.json naming conventions before creating any database or environment.
 7. Use the pipeline software -- never hack around it. If it cannot do the job, fix the software.
-At session start and after any interruption, re-read governance.json and devops.json before writing code. This is a pre-execution gate with no exceptions unless Boss grants memorialized authorization.</t>
+At session start and after any interruption, re-read governance.json and devops.json before writing code. This is a pre-execution gate with no exceptions unless human grants memorialized authorization.</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
@@ -3381,7 +3381,7 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>Before creating any new rule, requirement, story, feature, epic, or roadmap item, search all existing items for contradictions or duplicates. If a contradiction or duplicate is found, escalate to Boss before proceeding. This rule applies when loading the brain and when inserting or updating any rule. Implies a tool or function for rule insertion that enforces this gate.</t>
+          <t>Before creating any new rule, requirement, story, feature, epic, or roadmap item, search all existing items for contradictions or duplicates. If a contradiction or duplicate is found, escalate to human before proceeding. This rule applies when loading the brain and when inserting or updating any rule. Implies a tool or function for rule insertion that enforces this gate.</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
